--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -469,21 +469,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -504,11 +504,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,21 +519,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,16 +624,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>跳过的单元格总数</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>错误数</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>0</v>
       </c>
     </row>

--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>

--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>

--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>

--- a/test_config_sync/sync_report.xlsx
+++ b/test_config_sync/sync_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同步记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计信息" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test2.xlsx</t>
+          <t>test1.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test1.xlsx</t>
+          <t>test2.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
